--- a/test.xlsx
+++ b/test.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CNTT" sheetId="1" state="visible" r:id="rId1"/>
@@ -504,18 +504,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I808"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
-    <col width="4.140625" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="4.109375" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
+    <col width="13.33203125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
     <col width="28" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="15.42578125" customWidth="1" style="1" min="4" max="4"/>
-    <col width="30.42578125" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
-    <col width="20.5703125" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
-    <col width="28.140625" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
-    <col width="20.28515625" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
-    <col width="14.42578125" customWidth="1" style="1" min="9" max="16"/>
-    <col width="14.42578125" customWidth="1" style="1" min="17" max="16384"/>
+    <col width="15.44140625" customWidth="1" style="1" min="4" max="4"/>
+    <col width="30.44140625" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
+    <col width="20.5546875" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="28.109375" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
+    <col width="20.33203125" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
+    <col width="14.44140625" customWidth="1" style="1" min="9" max="17"/>
+    <col width="14.44140625" customWidth="1" style="1" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -592,10 +592,14 @@
       </c>
       <c r="F2" s="29" t="inlineStr">
         <is>
-          <t>Không tìm thấy</t>
+          <t>Không thể gửi</t>
         </is>
       </c>
-      <c r="G2" s="32" t="n"/>
+      <c r="G2" s="32" t="inlineStr">
+        <is>
+          <t>Chặn người lạ tìm số</t>
+        </is>
+      </c>
       <c r="H2" s="33" t="n"/>
       <c r="I2" s="17" t="n"/>
     </row>
@@ -631,7 +635,11 @@
           <t>Đã gửi</t>
         </is>
       </c>
-      <c r="G3" s="39" t="n"/>
+      <c r="G3" s="39" t="inlineStr">
+        <is>
+          <t>Đợi trả lời</t>
+        </is>
+      </c>
       <c r="H3" s="40" t="n"/>
       <c r="I3" s="25" t="n"/>
     </row>
@@ -664,10 +672,14 @@
       </c>
       <c r="F4" s="29" t="inlineStr">
         <is>
-          <t>Chặn người lạ</t>
+          <t>Đã gửi</t>
         </is>
       </c>
-      <c r="G4" s="32" t="n"/>
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>Không nhận tin nhắn người lạ</t>
+        </is>
+      </c>
       <c r="H4" s="33" t="n"/>
       <c r="I4" s="17" t="n"/>
     </row>

--- a/test.xlsx
+++ b/test.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,28 +161,7 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -514,8 +493,8 @@
     <col width="20.5546875" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
     <col width="28.109375" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
     <col width="20.33203125" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
-    <col width="14.44140625" customWidth="1" style="1" min="9" max="17"/>
-    <col width="14.44140625" customWidth="1" style="1" min="18" max="16384"/>
+    <col width="14.44140625" customWidth="1" style="1" min="9" max="19"/>
+    <col width="14.44140625" customWidth="1" style="1" min="20" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -564,123 +543,123 @@
       </c>
     </row>
     <row r="2" ht="59.1" customHeight="1">
-      <c r="A2" s="27" t="n">
+      <c r="A2" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>10
 1058045</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>TRẦN LÊ TUẤN ANH
 CCCD:
 SĐT: 0862762694</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>0862762694</t>
         </is>
       </c>
-      <c r="E2" s="31" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>Công nghệ thông tin</t>
         </is>
       </c>
-      <c r="F2" s="29" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>Không thể gửi</t>
         </is>
       </c>
-      <c r="G2" s="32" t="inlineStr">
+      <c r="G2" s="25" t="inlineStr">
         <is>
           <t>Chặn người lạ tìm số</t>
         </is>
       </c>
-      <c r="H2" s="33" t="n"/>
+      <c r="H2" s="26" t="n"/>
       <c r="I2" s="17" t="n"/>
     </row>
     <row r="3" ht="59.1" customHeight="1">
-      <c r="A3" s="34" t="n">
+      <c r="A3" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>10
 1058057</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>DƯƠNG MINH NGHĨA
 CCCD:
 SĐT: 0826991658</t>
         </is>
       </c>
-      <c r="D3" s="37" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>0826991658</t>
         </is>
       </c>
-      <c r="E3" s="38" t="inlineStr">
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>Công nghệ thông tin</t>
         </is>
       </c>
-      <c r="F3" s="36" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>Đã gửi</t>
         </is>
       </c>
-      <c r="G3" s="39" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t>Đợi trả lời</t>
         </is>
       </c>
-      <c r="H3" s="40" t="n"/>
-      <c r="I3" s="25" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="19" t="n"/>
     </row>
     <row r="4" ht="59.1" customHeight="1">
-      <c r="A4" s="27" t="n">
+      <c r="A4" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>10
 1058066</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>LÊ NGUYỄN DUY KHOA
 CCCD:
 SĐT: 0908212683</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>0908212683</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Công nghệ thông tin</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>Đã gửi</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Không nhận tin nhắn người lạ</t>
         </is>
       </c>
-      <c r="H4" s="33" t="n"/>
+      <c r="H4" s="26" t="n"/>
       <c r="I4" s="17" t="n"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
